--- a/DATA/TRACKS/quick-challenge/mru-quick-challenge.xlsx
+++ b/DATA/TRACKS/quick-challenge/mru-quick-challenge.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw" sheetId="1" r:id="Rd11ac89535134c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw" sheetId="1" r:id="R52130285fa1441a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="2" r:id="R9606f1b714cb4293"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +20,7 @@
     <x:numFmt numFmtId="202" formatCode="#,##0"/>
     <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,6 +34,12 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF16324F"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -49,7 +56,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="8">
     <x:border>
       <x:left/>
       <x:right/>
@@ -86,11 +93,49 @@
       <x:bottom/>
       <x:diagonal/>
     </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FF16324F"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFA8BDCA"/>
+      </x:right>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA8BDCA"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFA8BDCA"/>
+      </x:right>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA8BDCA"/>
+      </x:left>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -138,6 +183,48 @@
     <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -166,6 +253,19 @@
     <x:tableColumn id="15" name="actual_hours"/>
     <x:tableColumn id="16" name="rework_hours"/>
     <x:tableColumn id="17" name="issue_tag"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DataDictionary" displayName="DataDictionary" ref="A5:D22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:D22"/>
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="Worksheet"/>
+    <x:tableColumn id="2" name="Column"/>
+    <x:tableColumn id="3" name="Type and units"/>
+    <x:tableColumn id="4" name="Meaning"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -6907,7 +7007,308 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96e943026b1f43e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re038e79f65904213"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF6B7E8F"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="85" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="10" customHeight="1">
+      <x:c r="A1" s="18"/>
+      <x:c r="B1" s="18"/>
+      <x:c r="C1" s="18"/>
+      <x:c r="D1" s="18"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="19" t="str">
+        <x:v>Data Dictionary</x:v>
+      </x:c>
+      <x:c r="B2" s="19"/>
+      <x:c r="C2" s="19"/>
+      <x:c r="D2" s="19"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>Quick Challenge</x:v>
+      </x:c>
+      <x:c r="B3" s="20"/>
+      <x:c r="C3" s="20"/>
+      <x:c r="D3" s="20"/>
+    </x:row>
+    <x:row r="4" ht="10" customHeight="1">
+      <x:c r="A4" s="18"/>
+      <x:c r="B4" s="18"/>
+      <x:c r="C4" s="18"/>
+      <x:c r="D4" s="18"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="25" t="str">
+        <x:v>Worksheet</x:v>
+      </x:c>
+      <x:c r="B5" s="26" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="C5" s="26" t="str">
+        <x:v>Type and units</x:v>
+      </x:c>
+      <x:c r="D5" s="27" t="str">
+        <x:v>Meaning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
+      <x:c r="A6" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B6" s="29" t="str">
+        <x:v>work_item_id</x:v>
+      </x:c>
+      <x:c r="C6" s="29" t="str">
+        <x:v>Text identifier</x:v>
+      </x:c>
+      <x:c r="D6" s="30" t="str">
+        <x:v>Identifier assigned to the completed task. The same task has the same identifier in the Portfolio Project work log.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
+      <x:c r="A7" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B7" s="29" t="str">
+        <x:v>completion_date</x:v>
+      </x:c>
+      <x:c r="C7" s="29" t="str">
+        <x:v>Date, YYYY-MM-DD</x:v>
+      </x:c>
+      <x:c r="D7" s="30" t="str">
+        <x:v>Date the task was completed. This is the completion date rather than the date of an individual AI prompt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
+      <x:c r="A8" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="str">
+        <x:v>campaign</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="str">
+        <x:v>Campaign associated with the task: Campaign 1 or Campaign 2.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
+      <x:c r="A9" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="str">
+        <x:v>department</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="str">
+        <x:v>Department responsible for the task. The business departments are Content, Creative, Marketing Operations, and Analytics.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="48" customHeight="1">
+      <x:c r="A10" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="str">
+        <x:v>employee</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="str">
+        <x:v>Fictional employee responsible for the task.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="48" customHeight="1">
+      <x:c r="A11" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B11" s="29" t="str">
+        <x:v>product</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="str">
+        <x:v>AI application used for the task: CampaignChat, CopyStudio, DataFlow, or InsightDesk. Each task uses one product.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B12" s="29" t="str">
+        <x:v>model</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="str">
+        <x:v>Fictional AI model used for the task: Lite or Pro. Each task uses one model.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B13" s="29" t="str">
+        <x:v>task_type</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="D13" s="30" t="str">
+        <x:v>Description of the work performed, such as Write ad copy or Draft email sequence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B14" s="29" t="str">
+        <x:v>prompt_count</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="str">
+        <x:v>Integer, prompts</x:v>
+      </x:c>
+      <x:c r="D14" s="30" t="str">
+        <x:v>Number of employee interactions with AI for this task, including the first attempt, followups, and corrections.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B15" s="29" t="str">
+        <x:v>input_tokens</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="str">
+        <x:v>Integer, tokens</x:v>
+      </x:c>
+      <x:c r="D15" s="30" t="str">
+        <x:v>Total text units sent to AI across the task's prompts, including instructions and supporting context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
+      <x:c r="A16" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B16" s="29" t="str">
+        <x:v>output_tokens</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="str">
+        <x:v>Integer, tokens</x:v>
+      </x:c>
+      <x:c r="D16" s="30" t="str">
+        <x:v>Total text units returned by AI across the task's prompts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48" customHeight="1">
+      <x:c r="A17" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B17" s="29" t="str">
+        <x:v>input_rate_usd_per_million</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="str">
+        <x:v>Decimal, USD per 1,000,000 input tokens</x:v>
+      </x:c>
+      <x:c r="D17" s="30" t="str">
+        <x:v>Price for the task's model to process one million input tokens.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1">
+      <x:c r="A18" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B18" s="29" t="str">
+        <x:v>output_rate_usd_per_million</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="str">
+        <x:v>Decimal, USD per 1,000,000 output tokens</x:v>
+      </x:c>
+      <x:c r="D18" s="30" t="str">
+        <x:v>Price for the task's model to produce one million output tokens.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
+      <x:c r="A19" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B19" s="29" t="str">
+        <x:v>baseline_hours</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="str">
+        <x:v>Decimal, hours</x:v>
+      </x:c>
+      <x:c r="D19" s="30" t="str">
+        <x:v>Estimated human effort to complete the same task at acceptable quality without AI.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="48" customHeight="1">
+      <x:c r="A20" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B20" s="29" t="str">
+        <x:v>actual_hours</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="str">
+        <x:v>Decimal, hours</x:v>
+      </x:c>
+      <x:c r="D20" s="30" t="str">
+        <x:v>Total human effort while using AI, including preparation, prompting, review, and rework.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B21" s="29" t="str">
+        <x:v>rework_hours</x:v>
+      </x:c>
+      <x:c r="C21" s="29" t="str">
+        <x:v>Decimal, hours</x:v>
+      </x:c>
+      <x:c r="D21" s="30" t="str">
+        <x:v>Portion of actual_hours spent correcting or redoing work. These hours are already included in actual_hours.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="48" customHeight="1">
+      <x:c r="A22" s="28" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="B22" s="29" t="str">
+        <x:v>issue_tag</x:v>
+      </x:c>
+      <x:c r="C22" s="29" t="str">
+        <x:v>Text category</x:v>
+      </x:c>
+      <x:c r="D22" s="30" t="str">
+        <x:v>Primary recorded issue: None, Unclear prompt, Brief changed, or Data problem. None means no issue was recorded.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re569226b27344df9"/>
   </x:tableParts>
 </x:worksheet>
 </file>